--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135917154</v>
       </c>
       <c r="B4" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101387</v>
+        <v>101404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101404</v>
+        <v>101406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101406</v>
+        <v>101407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135917154</v>
       </c>
       <c r="B4" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101407</v>
+        <v>101408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135917154</v>
       </c>
       <c r="B4" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101408</v>
+        <v>101414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135917154</v>
       </c>
       <c r="B4" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101414</v>
+        <v>101415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101415</v>
+        <v>101426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135917154</v>
       </c>
       <c r="B4" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101426</v>
+        <v>101439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101439</v>
+        <v>101440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135917154</v>
       </c>
       <c r="B4" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101440</v>
+        <v>101453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99605</v>
+        <v>99618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 43168-2024 artfynd.xlsx
+++ b/artfynd/A 43168-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135917156</v>
       </c>
       <c r="B2" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135917159</v>
       </c>
       <c r="B3" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135917155</v>
       </c>
       <c r="B5" t="n">
-        <v>101453</v>
+        <v>101454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135917158</v>
       </c>
       <c r="B6" t="n">
-        <v>99618</v>
+        <v>99619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135917157</v>
       </c>
       <c r="B7" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
